--- a/ANEXO 2.xlsx
+++ b/ANEXO 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Personal\Desktop\ANEXO 2\ANEXO 2 CON LISTA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Personal\Desktop\REGISTRO_TFG\ANEXO 2\ANEXO_2.git.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3F7054-1168-418C-9B64-F4BC46CDD850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3224BAFF-481F-4996-A290-98FA1B25CCAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="13740" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE ESTUDIANTES" sheetId="6" r:id="rId1"/>
@@ -33,6 +33,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1722,89 +1725,30 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1850,11 +1794,139 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1869,15 +1941,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1888,66 +1951,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3973,24 +3976,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="N1" s="78" t="s">
+      <c r="N1" s="122" t="s">
         <v>231</v>
       </c>
-      <c r="O1" s="79"/>
+      <c r="O1" s="123"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="N2" s="80"/>
-      <c r="O2" s="81"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="125"/>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="120" t="s">
         <v>230</v>
       </c>
-      <c r="N3" s="82"/>
-      <c r="O3" s="83"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="127"/>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="77"/>
+      <c r="B4" s="121"/>
       <c r="Q4" s="1"/>
       <c r="U4" s="57" t="str">
         <f>IFERROR(INDEX('LISTA DE ESTUDIANTES'!$C$2:$C$102, MATCH($N$10,'LISTA DE ESTUDIANTES'!B2:B102, 0)), " ")</f>
@@ -4002,12 +4005,12 @@
       <c r="B5" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="84" t="s">
+      <c r="C5" s="106" t="s">
         <v>228</v>
       </c>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="86"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="108"/>
       <c r="G5" s="64"/>
       <c r="H5" s="64"/>
       <c r="J5" s="3"/>
@@ -4026,10 +4029,10 @@
       <c r="B6" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="87"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="89"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="111"/>
       <c r="G6" s="64"/>
       <c r="H6" s="64"/>
       <c r="J6" s="6"/>
@@ -4040,12 +4043,12 @@
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="8"/>
-      <c r="S6" s="84" t="s">
+      <c r="S6" s="106" t="s">
         <v>225</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
-      <c r="V6" s="86"/>
+      <c r="T6" s="107"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="108"/>
     </row>
     <row r="7" spans="1:22" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
@@ -4054,26 +4057,26 @@
       <c r="B7" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="87"/>
-      <c r="D7" s="88"/>
-      <c r="E7" s="88"/>
-      <c r="F7" s="89"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="111"/>
       <c r="G7" s="64"/>
       <c r="H7" s="64"/>
       <c r="J7" s="16"/>
       <c r="K7" s="18"/>
       <c r="L7" s="18"/>
-      <c r="M7" s="131" t="s">
+      <c r="M7" s="119" t="s">
         <v>9</v>
       </c>
-      <c r="N7" s="131"/>
-      <c r="O7" s="131"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="119"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="8"/>
-      <c r="S7" s="87"/>
-      <c r="T7" s="88"/>
-      <c r="U7" s="88"/>
-      <c r="V7" s="89"/>
+      <c r="S7" s="109"/>
+      <c r="T7" s="110"/>
+      <c r="U7" s="110"/>
+      <c r="V7" s="111"/>
     </row>
     <row r="8" spans="1:22" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
@@ -4082,10 +4085,10 @@
       <c r="B8" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="90"/>
-      <c r="D8" s="91"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="92"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="113"/>
+      <c r="F8" s="114"/>
       <c r="G8" s="64"/>
       <c r="H8" s="64"/>
       <c r="J8" s="16"/>
@@ -4098,10 +4101,10 @@
       <c r="O8" s="18"/>
       <c r="P8" s="18"/>
       <c r="Q8" s="8"/>
-      <c r="S8" s="87"/>
-      <c r="T8" s="88"/>
-      <c r="U8" s="88"/>
-      <c r="V8" s="89"/>
+      <c r="S8" s="109"/>
+      <c r="T8" s="110"/>
+      <c r="U8" s="110"/>
+      <c r="V8" s="111"/>
     </row>
     <row r="9" spans="1:22" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
@@ -4110,30 +4113,30 @@
       <c r="B9" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="93" t="s">
+      <c r="C9" s="128" t="s">
         <v>229</v>
       </c>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="95"/>
+      <c r="D9" s="129"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="130"/>
       <c r="G9" s="64"/>
       <c r="H9" s="64"/>
       <c r="J9" s="16"/>
-      <c r="K9" s="132" t="s">
+      <c r="K9" s="102" t="s">
         <v>314</v>
       </c>
-      <c r="L9" s="133"/>
-      <c r="M9" s="133"/>
-      <c r="N9" s="133"/>
-      <c r="O9" s="134"/>
+      <c r="L9" s="103"/>
+      <c r="M9" s="103"/>
+      <c r="N9" s="103"/>
+      <c r="O9" s="104"/>
       <c r="P9" s="26" t="s">
         <v>0</v>
       </c>
       <c r="Q9" s="8"/>
-      <c r="S9" s="90"/>
-      <c r="T9" s="91"/>
-      <c r="U9" s="91"/>
-      <c r="V9" s="92"/>
+      <c r="S9" s="112"/>
+      <c r="T9" s="113"/>
+      <c r="U9" s="113"/>
+      <c r="V9" s="114"/>
     </row>
     <row r="10" spans="1:22" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
@@ -4142,33 +4145,33 @@
       <c r="B10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="96"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
-      <c r="F10" s="98"/>
+      <c r="C10" s="131"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="133"/>
       <c r="G10" s="64"/>
       <c r="H10" s="64"/>
       <c r="J10" s="16"/>
-      <c r="K10" s="116" t="s">
+      <c r="K10" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="L10" s="117"/>
-      <c r="M10" s="117"/>
-      <c r="N10" s="118" t="s">
+      <c r="L10" s="116"/>
+      <c r="M10" s="116"/>
+      <c r="N10" s="139" t="s">
         <v>245</v>
       </c>
-      <c r="O10" s="119"/>
+      <c r="O10" s="140"/>
       <c r="P10" s="58" t="str">
         <f>+ "Sección: " &amp;$U$4</f>
         <v>Sección: 8-1</v>
       </c>
       <c r="Q10" s="8"/>
-      <c r="S10" s="84" t="s">
+      <c r="S10" s="106" t="s">
         <v>226</v>
       </c>
-      <c r="T10" s="85"/>
-      <c r="U10" s="85"/>
-      <c r="V10" s="86"/>
+      <c r="T10" s="107"/>
+      <c r="U10" s="107"/>
+      <c r="V10" s="108"/>
     </row>
     <row r="11" spans="1:22" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
@@ -4177,32 +4180,32 @@
       <c r="B11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="96"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="97"/>
-      <c r="F11" s="98"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="133"/>
       <c r="G11" s="64"/>
       <c r="H11" s="64"/>
       <c r="J11" s="16"/>
-      <c r="K11" s="116" t="s">
+      <c r="K11" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="L11" s="117"/>
-      <c r="M11" s="117"/>
-      <c r="N11" s="129" t="str">
+      <c r="L11" s="116"/>
+      <c r="M11" s="116"/>
+      <c r="N11" s="117" t="str">
         <f>IFERROR(INDEX('LISTA DE ESTUDIANTES'!$E$2:$E$102,MATCH($N$10,'LISTA DE ESTUDIANTES'!$B$2:$B$102, 0)), " ")</f>
         <v>Revisar Expediente</v>
       </c>
-      <c r="O11" s="130"/>
+      <c r="O11" s="118"/>
       <c r="P11" s="27">
         <f ca="1">+TODAY()</f>
-        <v>45815</v>
+        <v>46158</v>
       </c>
       <c r="Q11" s="8"/>
-      <c r="S11" s="87"/>
-      <c r="T11" s="88"/>
-      <c r="U11" s="88"/>
-      <c r="V11" s="89"/>
+      <c r="S11" s="109"/>
+      <c r="T11" s="110"/>
+      <c r="U11" s="110"/>
+      <c r="V11" s="111"/>
     </row>
     <row r="12" spans="1:22" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
@@ -4211,18 +4214,18 @@
       <c r="B12" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="99"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="100"/>
-      <c r="F12" s="101"/>
+      <c r="C12" s="134"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="136"/>
       <c r="G12" s="64"/>
       <c r="H12" s="64"/>
       <c r="J12" s="16"/>
-      <c r="K12" s="121" t="s">
+      <c r="K12" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="122"/>
-      <c r="M12" s="123"/>
+      <c r="L12" s="100"/>
+      <c r="M12" s="101"/>
       <c r="N12" s="19" t="s">
         <v>315</v>
       </c>
@@ -4233,10 +4236,10 @@
         <v>316</v>
       </c>
       <c r="Q12" s="8"/>
-      <c r="S12" s="87"/>
-      <c r="T12" s="88"/>
-      <c r="U12" s="88"/>
-      <c r="V12" s="89"/>
+      <c r="S12" s="109"/>
+      <c r="T12" s="110"/>
+      <c r="U12" s="110"/>
+      <c r="V12" s="111"/>
     </row>
     <row r="13" spans="1:22" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
@@ -4248,19 +4251,19 @@
       <c r="J13" s="16"/>
       <c r="K13" s="60"/>
       <c r="L13" s="60"/>
-      <c r="M13" s="120" t="s">
+      <c r="M13" s="141" t="s">
         <v>7</v>
       </c>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120" t="s">
+      <c r="N13" s="141"/>
+      <c r="O13" s="141" t="s">
         <v>5</v>
       </c>
-      <c r="P13" s="120"/>
+      <c r="P13" s="141"/>
       <c r="Q13" s="8"/>
-      <c r="S13" s="90"/>
-      <c r="T13" s="91"/>
-      <c r="U13" s="91"/>
-      <c r="V13" s="92"/>
+      <c r="S13" s="112"/>
+      <c r="T13" s="113"/>
+      <c r="U13" s="113"/>
+      <c r="V13" s="114"/>
     </row>
     <row r="14" spans="1:22" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
@@ -4270,21 +4273,21 @@
         <v>30</v>
       </c>
       <c r="J14" s="16"/>
-      <c r="K14" s="121" t="s">
+      <c r="K14" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="L14" s="122"/>
-      <c r="M14" s="122"/>
-      <c r="N14" s="122"/>
-      <c r="O14" s="122"/>
-      <c r="P14" s="123"/>
+      <c r="L14" s="100"/>
+      <c r="M14" s="100"/>
+      <c r="N14" s="100"/>
+      <c r="O14" s="100"/>
+      <c r="P14" s="101"/>
       <c r="Q14" s="8"/>
-      <c r="S14" s="84" t="s">
+      <c r="S14" s="106" t="s">
         <v>227</v>
       </c>
-      <c r="T14" s="85"/>
-      <c r="U14" s="85"/>
-      <c r="V14" s="86"/>
+      <c r="T14" s="107"/>
+      <c r="U14" s="107"/>
+      <c r="V14" s="108"/>
     </row>
     <row r="15" spans="1:22" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
@@ -4294,23 +4297,23 @@
         <v>32</v>
       </c>
       <c r="J15" s="16"/>
-      <c r="K15" s="126" t="s">
+      <c r="K15" s="144" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="127"/>
-      <c r="M15" s="124" t="s">
+      <c r="L15" s="145"/>
+      <c r="M15" s="142" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="125"/>
+      <c r="N15" s="143"/>
       <c r="O15" s="29" t="s">
         <v>12</v>
       </c>
       <c r="P15" s="30"/>
       <c r="Q15" s="8"/>
-      <c r="S15" s="87"/>
-      <c r="T15" s="88"/>
-      <c r="U15" s="88"/>
-      <c r="V15" s="89"/>
+      <c r="S15" s="109"/>
+      <c r="T15" s="110"/>
+      <c r="U15" s="110"/>
+      <c r="V15" s="111"/>
     </row>
     <row r="16" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
@@ -4320,22 +4323,22 @@
         <v>34</v>
       </c>
       <c r="J16" s="16"/>
-      <c r="K16" s="104" t="s">
+      <c r="K16" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="L16" s="105"/>
-      <c r="M16" s="108" t="str">
+      <c r="L16" s="84"/>
+      <c r="M16" s="87" t="str">
         <f>IFERROR(INDEX($B$6:$B$18, MATCH(K16, $A$6:$A$18, 0)), " ")</f>
         <v xml:space="preserve">Reforzar cada logro por más pequeño que este sea. </v>
       </c>
-      <c r="N16" s="109"/>
-      <c r="O16" s="112"/>
-      <c r="P16" s="113"/>
+      <c r="N16" s="88"/>
+      <c r="O16" s="91"/>
+      <c r="P16" s="92"/>
       <c r="Q16" s="8"/>
-      <c r="S16" s="87"/>
-      <c r="T16" s="88"/>
-      <c r="U16" s="88"/>
-      <c r="V16" s="89"/>
+      <c r="S16" s="109"/>
+      <c r="T16" s="110"/>
+      <c r="U16" s="110"/>
+      <c r="V16" s="111"/>
     </row>
     <row r="17" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
@@ -4345,17 +4348,17 @@
         <v>36</v>
       </c>
       <c r="J17" s="16"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="107"/>
-      <c r="M17" s="110"/>
-      <c r="N17" s="111"/>
-      <c r="O17" s="114"/>
-      <c r="P17" s="115"/>
+      <c r="K17" s="85"/>
+      <c r="L17" s="86"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="90"/>
+      <c r="O17" s="93"/>
+      <c r="P17" s="94"/>
       <c r="Q17" s="8"/>
-      <c r="S17" s="90"/>
-      <c r="T17" s="91"/>
-      <c r="U17" s="91"/>
-      <c r="V17" s="92"/>
+      <c r="S17" s="112"/>
+      <c r="T17" s="113"/>
+      <c r="U17" s="113"/>
+      <c r="V17" s="114"/>
     </row>
     <row r="18" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
@@ -4365,17 +4368,17 @@
         <v>38</v>
       </c>
       <c r="J18" s="16"/>
-      <c r="K18" s="104" t="s">
+      <c r="K18" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="L18" s="105"/>
-      <c r="M18" s="108" t="str">
+      <c r="L18" s="84"/>
+      <c r="M18" s="87" t="str">
         <f>IFERROR(INDEX($B$6:$B$18, MATCH(K18, $A$6:$A$18, 0)), " ")</f>
         <v xml:space="preserve">Brindar acercamiento físico y las manifestaciones de apoyo. </v>
       </c>
-      <c r="N18" s="109"/>
-      <c r="O18" s="112"/>
-      <c r="P18" s="113"/>
+      <c r="N18" s="88"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="92"/>
       <c r="Q18" s="8"/>
     </row>
     <row r="19" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4383,12 +4386,12 @@
         <v>111</v>
       </c>
       <c r="J19" s="16"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="107"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="111"/>
-      <c r="O19" s="114"/>
-      <c r="P19" s="115"/>
+      <c r="K19" s="85"/>
+      <c r="L19" s="86"/>
+      <c r="M19" s="89"/>
+      <c r="N19" s="90"/>
+      <c r="O19" s="93"/>
+      <c r="P19" s="94"/>
       <c r="Q19" s="8"/>
     </row>
     <row r="20" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4399,17 +4402,17 @@
         <v>56</v>
       </c>
       <c r="J20" s="16"/>
-      <c r="K20" s="104" t="s">
+      <c r="K20" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="L20" s="105"/>
-      <c r="M20" s="108" t="str">
+      <c r="L20" s="84"/>
+      <c r="M20" s="87" t="str">
         <f>IFERROR(INDEX($B$6:$B$18, MATCH(K20, $A$6:$A$18, 0)), " ")</f>
         <v xml:space="preserve">Utilizar la tutoría entre compañeros. </v>
       </c>
-      <c r="N20" s="109"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="113"/>
+      <c r="N20" s="88"/>
+      <c r="O20" s="91"/>
+      <c r="P20" s="92"/>
       <c r="Q20" s="8"/>
     </row>
     <row r="21" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4420,12 +4423,12 @@
         <v>58</v>
       </c>
       <c r="J21" s="16"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="107"/>
-      <c r="M21" s="110"/>
-      <c r="N21" s="111"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="115"/>
+      <c r="K21" s="85"/>
+      <c r="L21" s="86"/>
+      <c r="M21" s="89"/>
+      <c r="N21" s="90"/>
+      <c r="O21" s="93"/>
+      <c r="P21" s="94"/>
       <c r="Q21" s="8"/>
     </row>
     <row r="22" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4436,18 +4439,18 @@
         <v>60</v>
       </c>
       <c r="J22" s="16"/>
-      <c r="K22" s="104" t="s">
+      <c r="K22" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="105"/>
-      <c r="M22" s="135" t="s">
+      <c r="L22" s="84"/>
+      <c r="M22" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="N22" s="136"/>
-      <c r="O22" s="135" t="s">
+      <c r="N22" s="96"/>
+      <c r="O22" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="P22" s="136"/>
+      <c r="P22" s="96"/>
       <c r="Q22" s="8"/>
     </row>
     <row r="23" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4458,12 +4461,12 @@
         <v>62</v>
       </c>
       <c r="J23" s="16"/>
-      <c r="K23" s="106"/>
-      <c r="L23" s="107"/>
-      <c r="M23" s="137"/>
-      <c r="N23" s="138"/>
-      <c r="O23" s="137"/>
-      <c r="P23" s="138"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="86"/>
+      <c r="M23" s="97"/>
+      <c r="N23" s="98"/>
+      <c r="O23" s="97"/>
+      <c r="P23" s="98"/>
       <c r="Q23" s="8"/>
     </row>
     <row r="24" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4474,17 +4477,17 @@
         <v>64</v>
       </c>
       <c r="J24" s="16"/>
-      <c r="K24" s="104" t="s">
+      <c r="K24" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="L24" s="105"/>
-      <c r="M24" s="108" t="str">
+      <c r="L24" s="84"/>
+      <c r="M24" s="87" t="str">
         <f>IFERROR(INDEX($B$20:$B$30, MATCH(K24, $A$20:$A$30, 0)), " ")</f>
         <v>Sentar al estudiante en un lugar donde tenga buena iluminación</v>
       </c>
-      <c r="N24" s="109"/>
-      <c r="O24" s="112"/>
-      <c r="P24" s="113"/>
+      <c r="N24" s="88"/>
+      <c r="O24" s="91"/>
+      <c r="P24" s="92"/>
       <c r="Q24" s="8"/>
     </row>
     <row r="25" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4495,12 +4498,12 @@
         <v>66</v>
       </c>
       <c r="J25" s="16"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="107"/>
-      <c r="M25" s="110"/>
-      <c r="N25" s="111"/>
-      <c r="O25" s="114"/>
-      <c r="P25" s="115"/>
+      <c r="K25" s="85"/>
+      <c r="L25" s="86"/>
+      <c r="M25" s="89"/>
+      <c r="N25" s="90"/>
+      <c r="O25" s="93"/>
+      <c r="P25" s="94"/>
       <c r="Q25" s="8"/>
     </row>
     <row r="26" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4511,17 +4514,17 @@
         <v>68</v>
       </c>
       <c r="J26" s="16"/>
-      <c r="K26" s="104" t="s">
+      <c r="K26" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="L26" s="105"/>
-      <c r="M26" s="108" t="str">
+      <c r="L26" s="84"/>
+      <c r="M26" s="87" t="str">
         <f t="shared" ref="M26" si="0">IFERROR(INDEX($B$20:$B$30, MATCH(K26, $A$20:$A$30, 0)), " ")</f>
         <v>Organizar el tiempo y del espacio para mejorar el clima organizacional.</v>
       </c>
-      <c r="N26" s="109"/>
-      <c r="O26" s="112"/>
-      <c r="P26" s="113"/>
+      <c r="N26" s="88"/>
+      <c r="O26" s="91"/>
+      <c r="P26" s="92"/>
       <c r="Q26" s="8"/>
     </row>
     <row r="27" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4532,12 +4535,12 @@
         <v>70</v>
       </c>
       <c r="J27" s="16"/>
-      <c r="K27" s="106"/>
-      <c r="L27" s="107"/>
-      <c r="M27" s="110"/>
-      <c r="N27" s="111"/>
-      <c r="O27" s="114"/>
-      <c r="P27" s="115"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="86"/>
+      <c r="M27" s="89"/>
+      <c r="N27" s="90"/>
+      <c r="O27" s="93"/>
+      <c r="P27" s="94"/>
       <c r="Q27" s="8"/>
     </row>
     <row r="28" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4548,17 +4551,17 @@
         <v>72</v>
       </c>
       <c r="J28" s="16"/>
-      <c r="K28" s="104" t="s">
+      <c r="K28" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="L28" s="105"/>
-      <c r="M28" s="108" t="str">
+      <c r="L28" s="84"/>
+      <c r="M28" s="87" t="str">
         <f t="shared" ref="M28" si="1">IFERROR(INDEX($B$20:$B$30, MATCH(K28, $A$20:$A$30, 0)), " ")</f>
         <v>Ubicar al estudiante cerca de compañeros que no se desconcentren.</v>
       </c>
-      <c r="N28" s="109"/>
-      <c r="O28" s="112"/>
-      <c r="P28" s="113"/>
+      <c r="N28" s="88"/>
+      <c r="O28" s="91"/>
+      <c r="P28" s="92"/>
       <c r="Q28" s="8"/>
     </row>
     <row r="29" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4569,12 +4572,12 @@
         <v>74</v>
       </c>
       <c r="J29" s="16"/>
-      <c r="K29" s="106"/>
-      <c r="L29" s="107"/>
-      <c r="M29" s="110"/>
-      <c r="N29" s="111"/>
-      <c r="O29" s="114"/>
-      <c r="P29" s="115"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="86"/>
+      <c r="M29" s="89"/>
+      <c r="N29" s="90"/>
+      <c r="O29" s="93"/>
+      <c r="P29" s="94"/>
       <c r="Q29" s="8"/>
     </row>
     <row r="30" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4585,28 +4588,28 @@
         <v>76</v>
       </c>
       <c r="J30" s="16"/>
-      <c r="K30" s="104" t="s">
+      <c r="K30" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="L30" s="105"/>
-      <c r="M30" s="135" t="s">
+      <c r="L30" s="84"/>
+      <c r="M30" s="95" t="s">
         <v>112</v>
       </c>
-      <c r="N30" s="136"/>
-      <c r="O30" s="135" t="s">
+      <c r="N30" s="96"/>
+      <c r="O30" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="P30" s="136"/>
+      <c r="P30" s="96"/>
       <c r="Q30" s="8"/>
     </row>
     <row r="31" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J31" s="16"/>
-      <c r="K31" s="106"/>
-      <c r="L31" s="107"/>
-      <c r="M31" s="137"/>
-      <c r="N31" s="138"/>
-      <c r="O31" s="137"/>
-      <c r="P31" s="138"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="86"/>
+      <c r="M31" s="97"/>
+      <c r="N31" s="98"/>
+      <c r="O31" s="97"/>
+      <c r="P31" s="98"/>
       <c r="Q31" s="8"/>
     </row>
     <row r="32" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4615,17 +4618,17 @@
         <v>77</v>
       </c>
       <c r="J32" s="16"/>
-      <c r="K32" s="104" t="s">
+      <c r="K32" s="83" t="s">
         <v>89</v>
       </c>
-      <c r="L32" s="105"/>
-      <c r="M32" s="108" t="str">
+      <c r="L32" s="84"/>
+      <c r="M32" s="87" t="str">
         <f>IFERROR(INDEX($B$33:$B$49, MATCH(K32, $A$33:$A$49, 0)), " ")</f>
         <v>Usar láminas, mapas, gráficos y vídeos relacionados con los aprendizajes que se desarrollan.</v>
       </c>
-      <c r="N32" s="109"/>
-      <c r="O32" s="112"/>
-      <c r="P32" s="113"/>
+      <c r="N32" s="88"/>
+      <c r="O32" s="91"/>
+      <c r="P32" s="92"/>
       <c r="Q32" s="8"/>
     </row>
     <row r="33" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4636,12 +4639,12 @@
         <v>78</v>
       </c>
       <c r="J33" s="16"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="107"/>
-      <c r="M33" s="110"/>
-      <c r="N33" s="111"/>
-      <c r="O33" s="114"/>
-      <c r="P33" s="115"/>
+      <c r="K33" s="85"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="89"/>
+      <c r="N33" s="90"/>
+      <c r="O33" s="93"/>
+      <c r="P33" s="94"/>
       <c r="Q33" s="8"/>
     </row>
     <row r="34" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4652,17 +4655,17 @@
         <v>80</v>
       </c>
       <c r="J34" s="16"/>
-      <c r="K34" s="104" t="s">
+      <c r="K34" s="83" t="s">
         <v>103</v>
       </c>
-      <c r="L34" s="105"/>
-      <c r="M34" s="108" t="str">
+      <c r="L34" s="84"/>
+      <c r="M34" s="87" t="str">
         <f>IFERROR(INDEX($B$33:$B$49, MATCH(K34, $A$33:$A$49, 0)), " ")</f>
         <v>Facilitar material de reforzamiento para hacer en casa.</v>
       </c>
-      <c r="N34" s="109"/>
-      <c r="O34" s="112"/>
-      <c r="P34" s="113"/>
+      <c r="N34" s="88"/>
+      <c r="O34" s="91"/>
+      <c r="P34" s="92"/>
       <c r="Q34" s="8"/>
     </row>
     <row r="35" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4673,12 +4676,12 @@
         <v>82</v>
       </c>
       <c r="J35" s="16"/>
-      <c r="K35" s="106"/>
-      <c r="L35" s="107"/>
-      <c r="M35" s="110"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="114"/>
-      <c r="P35" s="115"/>
+      <c r="K35" s="85"/>
+      <c r="L35" s="86"/>
+      <c r="M35" s="89"/>
+      <c r="N35" s="90"/>
+      <c r="O35" s="93"/>
+      <c r="P35" s="94"/>
       <c r="Q35" s="8"/>
     </row>
     <row r="36" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4689,17 +4692,17 @@
         <v>84</v>
       </c>
       <c r="J36" s="16"/>
-      <c r="K36" s="104" t="s">
+      <c r="K36" s="83" t="s">
         <v>75</v>
       </c>
-      <c r="L36" s="105"/>
-      <c r="M36" s="108" t="str">
+      <c r="L36" s="84"/>
+      <c r="M36" s="87" t="str">
         <f>IFERROR(INDEX($B$33:$B$49, MATCH(K36, $A$33:$A$49, 0)), " ")</f>
         <v>Ampliar la letra al tamaño que el estudiante sienta mejor.</v>
       </c>
-      <c r="N36" s="109"/>
-      <c r="O36" s="112"/>
-      <c r="P36" s="113"/>
+      <c r="N36" s="88"/>
+      <c r="O36" s="91"/>
+      <c r="P36" s="92"/>
       <c r="Q36" s="8"/>
     </row>
     <row r="37" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4710,12 +4713,12 @@
         <v>86</v>
       </c>
       <c r="J37" s="16"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="107"/>
-      <c r="M37" s="110"/>
-      <c r="N37" s="111"/>
-      <c r="O37" s="114"/>
-      <c r="P37" s="115"/>
+      <c r="K37" s="85"/>
+      <c r="L37" s="86"/>
+      <c r="M37" s="89"/>
+      <c r="N37" s="90"/>
+      <c r="O37" s="93"/>
+      <c r="P37" s="94"/>
       <c r="Q37" s="8"/>
     </row>
     <row r="38" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4766,18 +4769,18 @@
         <v>94</v>
       </c>
       <c r="J41" s="16"/>
-      <c r="K41" s="104" t="s">
+      <c r="K41" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="L41" s="105"/>
-      <c r="M41" s="135" t="s">
+      <c r="L41" s="84"/>
+      <c r="M41" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="N41" s="136"/>
-      <c r="O41" s="135" t="s">
+      <c r="N41" s="96"/>
+      <c r="O41" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="P41" s="136"/>
+      <c r="P41" s="96"/>
       <c r="Q41" s="8"/>
     </row>
     <row r="42" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4788,12 +4791,12 @@
         <v>96</v>
       </c>
       <c r="J42" s="16"/>
-      <c r="K42" s="106"/>
-      <c r="L42" s="107"/>
-      <c r="M42" s="137"/>
-      <c r="N42" s="138"/>
-      <c r="O42" s="137"/>
-      <c r="P42" s="138"/>
+      <c r="K42" s="85"/>
+      <c r="L42" s="86"/>
+      <c r="M42" s="97"/>
+      <c r="N42" s="98"/>
+      <c r="O42" s="97"/>
+      <c r="P42" s="98"/>
       <c r="Q42" s="8"/>
     </row>
     <row r="43" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4804,17 +4807,17 @@
         <v>98</v>
       </c>
       <c r="J43" s="16"/>
-      <c r="K43" s="104" t="s">
+      <c r="K43" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="L43" s="105"/>
-      <c r="M43" s="108" t="str">
+      <c r="L43" s="84"/>
+      <c r="M43" s="87" t="str">
         <f>IFERROR(INDEX($B$53:$B$87, MATCH(K43, $A$53:$A$87, 0)), " ")</f>
         <v>Hablar siempre frente al estudiante (contacto visual).</v>
       </c>
-      <c r="N43" s="109"/>
-      <c r="O43" s="112"/>
-      <c r="P43" s="113"/>
+      <c r="N43" s="88"/>
+      <c r="O43" s="91"/>
+      <c r="P43" s="92"/>
       <c r="Q43" s="8"/>
     </row>
     <row r="44" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4825,12 +4828,12 @@
         <v>100</v>
       </c>
       <c r="J44" s="16"/>
-      <c r="K44" s="106"/>
-      <c r="L44" s="107"/>
-      <c r="M44" s="110"/>
-      <c r="N44" s="111"/>
-      <c r="O44" s="114"/>
-      <c r="P44" s="115"/>
+      <c r="K44" s="85"/>
+      <c r="L44" s="86"/>
+      <c r="M44" s="89"/>
+      <c r="N44" s="90"/>
+      <c r="O44" s="93"/>
+      <c r="P44" s="94"/>
       <c r="Q44" s="8"/>
     </row>
     <row r="45" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4841,17 +4844,17 @@
         <v>102</v>
       </c>
       <c r="J45" s="16"/>
-      <c r="K45" s="104" t="s">
+      <c r="K45" s="83" t="s">
         <v>126</v>
       </c>
-      <c r="L45" s="105"/>
-      <c r="M45" s="108" t="str">
+      <c r="L45" s="84"/>
+      <c r="M45" s="87" t="str">
         <f t="shared" ref="M45" si="2">IFERROR(INDEX($B$53:$B$87, MATCH(K45, $A$53:$A$87, 0)), " ")</f>
         <v>De ser necesario disminuir la longitud y la cantidad de las tareas y/o actividades.</v>
       </c>
-      <c r="N45" s="109"/>
-      <c r="O45" s="112"/>
-      <c r="P45" s="113"/>
+      <c r="N45" s="88"/>
+      <c r="O45" s="91"/>
+      <c r="P45" s="92"/>
       <c r="Q45" s="8"/>
     </row>
     <row r="46" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4862,12 +4865,12 @@
         <v>104</v>
       </c>
       <c r="J46" s="16"/>
-      <c r="K46" s="106"/>
-      <c r="L46" s="107"/>
-      <c r="M46" s="110"/>
-      <c r="N46" s="111"/>
-      <c r="O46" s="114"/>
-      <c r="P46" s="115"/>
+      <c r="K46" s="85"/>
+      <c r="L46" s="86"/>
+      <c r="M46" s="89"/>
+      <c r="N46" s="90"/>
+      <c r="O46" s="93"/>
+      <c r="P46" s="94"/>
       <c r="Q46" s="8"/>
     </row>
     <row r="47" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4878,17 +4881,17 @@
         <v>106</v>
       </c>
       <c r="J47" s="16"/>
-      <c r="K47" s="104" t="s">
+      <c r="K47" s="83" t="s">
         <v>174</v>
       </c>
-      <c r="L47" s="105"/>
-      <c r="M47" s="108" t="str">
+      <c r="L47" s="84"/>
+      <c r="M47" s="87" t="str">
         <f t="shared" ref="M47" si="3">IFERROR(INDEX($B$53:$B$87, MATCH(K47, $A$53:$A$87, 0)), " ")</f>
         <v>Establecer rutinas de trabajo.</v>
       </c>
-      <c r="N47" s="109"/>
-      <c r="O47" s="112"/>
-      <c r="P47" s="113"/>
+      <c r="N47" s="88"/>
+      <c r="O47" s="91"/>
+      <c r="P47" s="92"/>
       <c r="Q47" s="8"/>
     </row>
     <row r="48" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4899,12 +4902,12 @@
         <v>108</v>
       </c>
       <c r="J48" s="16"/>
-      <c r="K48" s="106"/>
-      <c r="L48" s="107"/>
-      <c r="M48" s="110"/>
-      <c r="N48" s="111"/>
-      <c r="O48" s="114"/>
-      <c r="P48" s="115"/>
+      <c r="K48" s="85"/>
+      <c r="L48" s="86"/>
+      <c r="M48" s="89"/>
+      <c r="N48" s="90"/>
+      <c r="O48" s="93"/>
+      <c r="P48" s="94"/>
       <c r="Q48" s="8"/>
     </row>
     <row r="49" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4915,43 +4918,43 @@
         <v>76</v>
       </c>
       <c r="J49" s="16"/>
-      <c r="K49" s="104" t="s">
+      <c r="K49" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="L49" s="105"/>
-      <c r="M49" s="135" t="s">
+      <c r="L49" s="84"/>
+      <c r="M49" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="N49" s="136"/>
-      <c r="O49" s="135" t="s">
+      <c r="N49" s="96"/>
+      <c r="O49" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="P49" s="136"/>
+      <c r="P49" s="96"/>
       <c r="Q49" s="8"/>
     </row>
     <row r="50" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J50" s="16"/>
-      <c r="K50" s="106"/>
-      <c r="L50" s="107"/>
-      <c r="M50" s="137"/>
-      <c r="N50" s="138"/>
-      <c r="O50" s="137"/>
-      <c r="P50" s="138"/>
+      <c r="K50" s="85"/>
+      <c r="L50" s="86"/>
+      <c r="M50" s="97"/>
+      <c r="N50" s="98"/>
+      <c r="O50" s="97"/>
+      <c r="P50" s="98"/>
       <c r="Q50" s="8"/>
     </row>
     <row r="51" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J51" s="16"/>
-      <c r="K51" s="104" t="s">
+      <c r="K51" s="83" t="s">
         <v>208</v>
       </c>
-      <c r="L51" s="105"/>
-      <c r="M51" s="108" t="str">
+      <c r="L51" s="84"/>
+      <c r="M51" s="87" t="str">
         <f>IFERROR(INDEX($B$90:$B$104, MATCH(K51, $A$90:$A$104, 0)), " ")</f>
         <v>Usar la calculadora.</v>
       </c>
-      <c r="N51" s="109"/>
-      <c r="O51" s="112"/>
-      <c r="P51" s="113"/>
+      <c r="N51" s="88"/>
+      <c r="O51" s="91"/>
+      <c r="P51" s="92"/>
       <c r="Q51" s="8"/>
     </row>
     <row r="52" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4960,12 +4963,12 @@
         <v>113</v>
       </c>
       <c r="J52" s="6"/>
-      <c r="K52" s="106"/>
-      <c r="L52" s="107"/>
-      <c r="M52" s="110"/>
-      <c r="N52" s="111"/>
-      <c r="O52" s="114"/>
-      <c r="P52" s="115"/>
+      <c r="K52" s="85"/>
+      <c r="L52" s="86"/>
+      <c r="M52" s="89"/>
+      <c r="N52" s="90"/>
+      <c r="O52" s="93"/>
+      <c r="P52" s="94"/>
       <c r="Q52" s="2"/>
     </row>
     <row r="53" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4976,17 +4979,17 @@
         <v>115</v>
       </c>
       <c r="J53" s="6"/>
-      <c r="K53" s="104" t="s">
+      <c r="K53" s="83" t="s">
         <v>198</v>
       </c>
-      <c r="L53" s="105"/>
-      <c r="M53" s="108" t="str">
+      <c r="L53" s="84"/>
+      <c r="M53" s="87" t="str">
         <f t="shared" ref="M53" si="4">IFERROR(INDEX($B$90:$B$104, MATCH(K53, $A$90:$A$104, 0)), " ")</f>
         <v>Aplicar evaluaciones cortas y frecuentes.</v>
       </c>
-      <c r="N53" s="109"/>
-      <c r="O53" s="112"/>
-      <c r="P53" s="113"/>
+      <c r="N53" s="88"/>
+      <c r="O53" s="91"/>
+      <c r="P53" s="92"/>
       <c r="Q53" s="2"/>
     </row>
     <row r="54" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4997,12 +5000,12 @@
         <v>117</v>
       </c>
       <c r="J54" s="6"/>
-      <c r="K54" s="106"/>
-      <c r="L54" s="107"/>
-      <c r="M54" s="110"/>
-      <c r="N54" s="111"/>
-      <c r="O54" s="114"/>
-      <c r="P54" s="115"/>
+      <c r="K54" s="85"/>
+      <c r="L54" s="86"/>
+      <c r="M54" s="89"/>
+      <c r="N54" s="90"/>
+      <c r="O54" s="93"/>
+      <c r="P54" s="94"/>
       <c r="Q54" s="2"/>
     </row>
     <row r="55" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5013,17 +5016,17 @@
         <v>119</v>
       </c>
       <c r="J55" s="6"/>
-      <c r="K55" s="104" t="s">
+      <c r="K55" s="83" t="s">
         <v>208</v>
       </c>
-      <c r="L55" s="105"/>
-      <c r="M55" s="108" t="str">
+      <c r="L55" s="84"/>
+      <c r="M55" s="87" t="str">
         <f t="shared" ref="M55" si="5">IFERROR(INDEX($B$90:$B$104, MATCH(K55, $A$90:$A$104, 0)), " ")</f>
         <v>Usar la calculadora.</v>
       </c>
-      <c r="N55" s="109"/>
-      <c r="O55" s="112"/>
-      <c r="P55" s="113"/>
+      <c r="N55" s="88"/>
+      <c r="O55" s="91"/>
+      <c r="P55" s="92"/>
       <c r="Q55" s="2"/>
     </row>
     <row r="56" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5034,12 +5037,12 @@
         <v>121</v>
       </c>
       <c r="J56" s="6"/>
-      <c r="K56" s="106"/>
-      <c r="L56" s="107"/>
-      <c r="M56" s="110"/>
-      <c r="N56" s="111"/>
-      <c r="O56" s="114"/>
-      <c r="P56" s="115"/>
+      <c r="K56" s="85"/>
+      <c r="L56" s="86"/>
+      <c r="M56" s="89"/>
+      <c r="N56" s="90"/>
+      <c r="O56" s="93"/>
+      <c r="P56" s="94"/>
       <c r="Q56" s="2"/>
     </row>
     <row r="57" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5066,14 +5069,14 @@
         <v>125</v>
       </c>
       <c r="J58" s="6"/>
-      <c r="K58" s="144" t="s">
+      <c r="K58" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="L58" s="144"/>
-      <c r="M58" s="144"/>
-      <c r="N58" s="144"/>
-      <c r="O58" s="144"/>
-      <c r="P58" s="144"/>
+      <c r="L58" s="81"/>
+      <c r="M58" s="81"/>
+      <c r="N58" s="81"/>
+      <c r="O58" s="81"/>
+      <c r="P58" s="81"/>
       <c r="Q58" s="2"/>
     </row>
     <row r="59" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5084,11 +5087,11 @@
         <v>127</v>
       </c>
       <c r="J59" s="6"/>
-      <c r="K59" s="145" t="s">
+      <c r="K59" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="L59" s="145"/>
-      <c r="M59" s="145"/>
+      <c r="L59" s="82"/>
+      <c r="M59" s="82"/>
       <c r="N59" s="31" t="s">
         <v>47</v>
       </c>
@@ -5144,12 +5147,12 @@
         <v>133</v>
       </c>
       <c r="J62" s="6"/>
-      <c r="K62" s="139"/>
-      <c r="L62" s="140"/>
-      <c r="M62" s="140"/>
-      <c r="N62" s="140"/>
-      <c r="O62" s="140"/>
-      <c r="P62" s="141"/>
+      <c r="K62" s="76"/>
+      <c r="L62" s="77"/>
+      <c r="M62" s="77"/>
+      <c r="N62" s="77"/>
+      <c r="O62" s="77"/>
+      <c r="P62" s="78"/>
       <c r="Q62" s="2"/>
     </row>
     <row r="63" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5160,12 +5163,12 @@
         <v>135</v>
       </c>
       <c r="J63" s="6"/>
-      <c r="K63" s="139"/>
-      <c r="L63" s="140"/>
-      <c r="M63" s="140"/>
-      <c r="N63" s="140"/>
-      <c r="O63" s="140"/>
-      <c r="P63" s="141"/>
+      <c r="K63" s="76"/>
+      <c r="L63" s="77"/>
+      <c r="M63" s="77"/>
+      <c r="N63" s="77"/>
+      <c r="O63" s="77"/>
+      <c r="P63" s="78"/>
       <c r="Q63" s="2"/>
     </row>
     <row r="64" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5176,12 +5179,12 @@
         <v>137</v>
       </c>
       <c r="J64" s="6"/>
-      <c r="K64" s="139"/>
-      <c r="L64" s="140"/>
-      <c r="M64" s="140"/>
-      <c r="N64" s="140"/>
-      <c r="O64" s="140"/>
-      <c r="P64" s="141"/>
+      <c r="K64" s="76"/>
+      <c r="L64" s="77"/>
+      <c r="M64" s="77"/>
+      <c r="N64" s="77"/>
+      <c r="O64" s="77"/>
+      <c r="P64" s="78"/>
       <c r="Q64" s="8"/>
     </row>
     <row r="65" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5228,17 +5231,17 @@
         <v>143</v>
       </c>
       <c r="J67" s="6"/>
-      <c r="K67" s="142" t="s">
+      <c r="K67" s="79" t="s">
         <v>49</v>
       </c>
-      <c r="L67" s="142"/>
-      <c r="M67" s="142"/>
-      <c r="N67" s="142"/>
-      <c r="O67" s="142" t="s">
+      <c r="L67" s="79"/>
+      <c r="M67" s="79"/>
+      <c r="N67" s="79"/>
+      <c r="O67" s="79" t="s">
         <v>51</v>
       </c>
-      <c r="P67" s="142"/>
-      <c r="Q67" s="143"/>
+      <c r="P67" s="79"/>
+      <c r="Q67" s="80"/>
     </row>
     <row r="68" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="13" t="s">
@@ -5330,15 +5333,15 @@
         <v>155</v>
       </c>
       <c r="J73" s="6"/>
-      <c r="K73" s="102" t="s">
+      <c r="K73" s="137" t="s">
         <v>53</v>
       </c>
-      <c r="L73" s="102"/>
-      <c r="M73" s="102"/>
-      <c r="N73" s="102"/>
-      <c r="O73" s="102"/>
-      <c r="P73" s="102"/>
-      <c r="Q73" s="103"/>
+      <c r="L73" s="137"/>
+      <c r="M73" s="137"/>
+      <c r="N73" s="137"/>
+      <c r="O73" s="137"/>
+      <c r="P73" s="137"/>
+      <c r="Q73" s="138"/>
     </row>
     <row r="74" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="13" t="s">
@@ -5350,12 +5353,12 @@
       <c r="J74" s="9"/>
       <c r="K74" s="10"/>
       <c r="L74" s="10"/>
-      <c r="M74" s="128" t="s">
+      <c r="M74" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="N74" s="128"/>
-      <c r="O74" s="128"/>
-      <c r="P74" s="128"/>
+      <c r="N74" s="105"/>
+      <c r="O74" s="105"/>
+      <c r="P74" s="105"/>
       <c r="Q74" s="11"/>
     </row>
     <row r="75" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5686,25 +5689,56 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="TZ2GIgc+/GCtl/EnGbpqyNzBabNY+ThsrI4pBI7/yNykn/OakjiUwYI3G8imVfDwTFeC5yBw1reR9TobeyHzEA==" saltValue="u5O4E4/F8PQaZyB6KZHOwA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="85">
-    <mergeCell ref="K63:P63"/>
-    <mergeCell ref="K67:N67"/>
-    <mergeCell ref="O67:Q67"/>
-    <mergeCell ref="K64:P64"/>
-    <mergeCell ref="K58:P58"/>
-    <mergeCell ref="K59:M59"/>
-    <mergeCell ref="K62:P62"/>
-    <mergeCell ref="K53:L54"/>
-    <mergeCell ref="M53:N54"/>
-    <mergeCell ref="O53:P54"/>
-    <mergeCell ref="K55:L56"/>
-    <mergeCell ref="M55:N56"/>
-    <mergeCell ref="O55:P56"/>
-    <mergeCell ref="K49:L50"/>
-    <mergeCell ref="M49:N50"/>
-    <mergeCell ref="O49:P50"/>
-    <mergeCell ref="K51:L52"/>
-    <mergeCell ref="M51:N52"/>
-    <mergeCell ref="O51:P52"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="N1:O3"/>
+    <mergeCell ref="C5:F8"/>
+    <mergeCell ref="C9:F12"/>
+    <mergeCell ref="K73:Q73"/>
+    <mergeCell ref="K18:L19"/>
+    <mergeCell ref="M18:N19"/>
+    <mergeCell ref="O16:P17"/>
+    <mergeCell ref="O18:P19"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M74:P74"/>
+    <mergeCell ref="S6:V9"/>
+    <mergeCell ref="S10:V13"/>
+    <mergeCell ref="S14:V17"/>
+    <mergeCell ref="K36:L37"/>
+    <mergeCell ref="K41:L42"/>
+    <mergeCell ref="K43:L44"/>
+    <mergeCell ref="K45:L46"/>
+    <mergeCell ref="K47:L48"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="K30:L31"/>
+    <mergeCell ref="K32:L33"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="K16:L17"/>
+    <mergeCell ref="M16:N17"/>
+    <mergeCell ref="K14:P14"/>
+    <mergeCell ref="K9:O9"/>
+    <mergeCell ref="K20:L21"/>
+    <mergeCell ref="K22:L23"/>
+    <mergeCell ref="K24:L25"/>
+    <mergeCell ref="K26:L27"/>
+    <mergeCell ref="K28:L29"/>
+    <mergeCell ref="M36:N37"/>
+    <mergeCell ref="M41:N42"/>
+    <mergeCell ref="K34:L35"/>
+    <mergeCell ref="M30:N31"/>
+    <mergeCell ref="M32:N33"/>
+    <mergeCell ref="M43:N44"/>
+    <mergeCell ref="M20:N21"/>
+    <mergeCell ref="M22:N23"/>
+    <mergeCell ref="M24:N25"/>
+    <mergeCell ref="M26:N27"/>
+    <mergeCell ref="M28:N29"/>
     <mergeCell ref="M45:N46"/>
     <mergeCell ref="M47:N48"/>
     <mergeCell ref="O20:P21"/>
@@ -5721,56 +5755,25 @@
     <mergeCell ref="O45:P46"/>
     <mergeCell ref="O47:P48"/>
     <mergeCell ref="M34:N35"/>
-    <mergeCell ref="M43:N44"/>
-    <mergeCell ref="M20:N21"/>
-    <mergeCell ref="M22:N23"/>
-    <mergeCell ref="M24:N25"/>
-    <mergeCell ref="M26:N27"/>
-    <mergeCell ref="M28:N29"/>
-    <mergeCell ref="K26:L27"/>
-    <mergeCell ref="K28:L29"/>
-    <mergeCell ref="M36:N37"/>
-    <mergeCell ref="M41:N42"/>
-    <mergeCell ref="K34:L35"/>
-    <mergeCell ref="M30:N31"/>
-    <mergeCell ref="M32:N33"/>
-    <mergeCell ref="K14:P14"/>
-    <mergeCell ref="K9:O9"/>
-    <mergeCell ref="K20:L21"/>
-    <mergeCell ref="K22:L23"/>
-    <mergeCell ref="K24:L25"/>
-    <mergeCell ref="M74:P74"/>
-    <mergeCell ref="S6:V9"/>
-    <mergeCell ref="S10:V13"/>
-    <mergeCell ref="S14:V17"/>
-    <mergeCell ref="K36:L37"/>
-    <mergeCell ref="K41:L42"/>
-    <mergeCell ref="K43:L44"/>
-    <mergeCell ref="K45:L46"/>
-    <mergeCell ref="K47:L48"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="K30:L31"/>
-    <mergeCell ref="K32:L33"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="K16:L17"/>
-    <mergeCell ref="M16:N17"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="N1:O3"/>
-    <mergeCell ref="C5:F8"/>
-    <mergeCell ref="C9:F12"/>
-    <mergeCell ref="K73:Q73"/>
-    <mergeCell ref="K18:L19"/>
-    <mergeCell ref="M18:N19"/>
-    <mergeCell ref="O16:P17"/>
-    <mergeCell ref="O18:P19"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K49:L50"/>
+    <mergeCell ref="M49:N50"/>
+    <mergeCell ref="O49:P50"/>
+    <mergeCell ref="K51:L52"/>
+    <mergeCell ref="M51:N52"/>
+    <mergeCell ref="O51:P52"/>
+    <mergeCell ref="K53:L54"/>
+    <mergeCell ref="M53:N54"/>
+    <mergeCell ref="O53:P54"/>
+    <mergeCell ref="K55:L56"/>
+    <mergeCell ref="M55:N56"/>
+    <mergeCell ref="O55:P56"/>
+    <mergeCell ref="K63:P63"/>
+    <mergeCell ref="K67:N67"/>
+    <mergeCell ref="O67:Q67"/>
+    <mergeCell ref="K64:P64"/>
+    <mergeCell ref="K58:P58"/>
+    <mergeCell ref="K59:M59"/>
+    <mergeCell ref="K62:P62"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="5">
@@ -5834,24 +5837,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="N1" s="78" t="s">
+      <c r="N1" s="122" t="s">
         <v>231</v>
       </c>
-      <c r="O1" s="79"/>
+      <c r="O1" s="123"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="N2" s="80"/>
-      <c r="O2" s="81"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="125"/>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="120" t="s">
         <v>230</v>
       </c>
-      <c r="N3" s="82"/>
-      <c r="O3" s="83"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="127"/>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="77"/>
+      <c r="B4" s="121"/>
       <c r="Q4" s="1"/>
       <c r="U4" s="57" t="str">
         <f>IFERROR(INDEX('LISTA DE ESTUDIANTES'!$C$2:$C$102, MATCH($N$10,'LISTA DE ESTUDIANTES'!B2:B102, 0)), " ")</f>
@@ -5863,12 +5866,12 @@
       <c r="B5" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="84" t="s">
+      <c r="C5" s="106" t="s">
         <v>228</v>
       </c>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="86"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="108"/>
       <c r="G5" s="75"/>
       <c r="H5" s="75"/>
       <c r="J5" s="3"/>
@@ -5887,10 +5890,10 @@
       <c r="B6" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="87"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="89"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="111"/>
       <c r="G6" s="75"/>
       <c r="H6" s="75"/>
       <c r="J6" s="6"/>
@@ -5901,12 +5904,12 @@
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="8"/>
-      <c r="S6" s="84" t="s">
+      <c r="S6" s="106" t="s">
         <v>225</v>
       </c>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
-      <c r="V6" s="86"/>
+      <c r="T6" s="107"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="108"/>
     </row>
     <row r="7" spans="1:22" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
@@ -5915,26 +5918,26 @@
       <c r="B7" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="87"/>
-      <c r="D7" s="88"/>
-      <c r="E7" s="88"/>
-      <c r="F7" s="89"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="111"/>
       <c r="G7" s="75"/>
       <c r="H7" s="75"/>
       <c r="J7" s="16"/>
       <c r="K7" s="18"/>
       <c r="L7" s="18"/>
-      <c r="M7" s="131" t="s">
+      <c r="M7" s="119" t="s">
         <v>9</v>
       </c>
-      <c r="N7" s="131"/>
-      <c r="O7" s="131"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="119"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="8"/>
-      <c r="S7" s="87"/>
-      <c r="T7" s="88"/>
-      <c r="U7" s="88"/>
-      <c r="V7" s="89"/>
+      <c r="S7" s="109"/>
+      <c r="T7" s="110"/>
+      <c r="U7" s="110"/>
+      <c r="V7" s="111"/>
     </row>
     <row r="8" spans="1:22" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
@@ -5943,10 +5946,10 @@
       <c r="B8" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="90"/>
-      <c r="D8" s="91"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="92"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="113"/>
+      <c r="F8" s="114"/>
       <c r="G8" s="75"/>
       <c r="H8" s="75"/>
       <c r="J8" s="16"/>
@@ -5959,10 +5962,10 @@
       <c r="O8" s="18"/>
       <c r="P8" s="18"/>
       <c r="Q8" s="8"/>
-      <c r="S8" s="87"/>
-      <c r="T8" s="88"/>
-      <c r="U8" s="88"/>
-      <c r="V8" s="89"/>
+      <c r="S8" s="109"/>
+      <c r="T8" s="110"/>
+      <c r="U8" s="110"/>
+      <c r="V8" s="111"/>
     </row>
     <row r="9" spans="1:22" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
@@ -5971,30 +5974,30 @@
       <c r="B9" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="93" t="s">
+      <c r="C9" s="128" t="s">
         <v>229</v>
       </c>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="95"/>
+      <c r="D9" s="129"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="130"/>
       <c r="G9" s="75"/>
       <c r="H9" s="75"/>
       <c r="J9" s="16"/>
-      <c r="K9" s="132" t="s">
+      <c r="K9" s="102" t="s">
         <v>314</v>
       </c>
-      <c r="L9" s="133"/>
-      <c r="M9" s="133"/>
-      <c r="N9" s="133"/>
-      <c r="O9" s="134"/>
+      <c r="L9" s="103"/>
+      <c r="M9" s="103"/>
+      <c r="N9" s="103"/>
+      <c r="O9" s="104"/>
       <c r="P9" s="26" t="s">
         <v>0</v>
       </c>
       <c r="Q9" s="8"/>
-      <c r="S9" s="90"/>
-      <c r="T9" s="91"/>
-      <c r="U9" s="91"/>
-      <c r="V9" s="92"/>
+      <c r="S9" s="112"/>
+      <c r="T9" s="113"/>
+      <c r="U9" s="113"/>
+      <c r="V9" s="114"/>
     </row>
     <row r="10" spans="1:22" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
@@ -6003,34 +6006,34 @@
       <c r="B10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="96"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
-      <c r="F10" s="98"/>
+      <c r="C10" s="131"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="133"/>
       <c r="G10" s="75"/>
       <c r="H10" s="75"/>
       <c r="J10" s="16"/>
-      <c r="K10" s="116" t="s">
+      <c r="K10" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="L10" s="117"/>
-      <c r="M10" s="117"/>
-      <c r="N10" s="118" t="str">
+      <c r="L10" s="116"/>
+      <c r="M10" s="116"/>
+      <c r="N10" s="139" t="str">
         <f>+'ESPAÑOL '!N10</f>
         <v>Caballero González Angie Guiselle</v>
       </c>
-      <c r="O10" s="119"/>
+      <c r="O10" s="140"/>
       <c r="P10" s="58" t="str">
         <f>+ "Sección: " &amp;$U$4</f>
         <v>Sección: 8-1</v>
       </c>
       <c r="Q10" s="8"/>
-      <c r="S10" s="84" t="s">
+      <c r="S10" s="106" t="s">
         <v>226</v>
       </c>
-      <c r="T10" s="85"/>
-      <c r="U10" s="85"/>
-      <c r="V10" s="86"/>
+      <c r="T10" s="107"/>
+      <c r="U10" s="107"/>
+      <c r="V10" s="108"/>
     </row>
     <row r="11" spans="1:22" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
@@ -6039,32 +6042,32 @@
       <c r="B11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="96"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="97"/>
-      <c r="F11" s="98"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="133"/>
       <c r="G11" s="75"/>
       <c r="H11" s="75"/>
       <c r="J11" s="16"/>
-      <c r="K11" s="116" t="s">
+      <c r="K11" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="L11" s="117"/>
-      <c r="M11" s="117"/>
-      <c r="N11" s="129" t="str">
+      <c r="L11" s="116"/>
+      <c r="M11" s="116"/>
+      <c r="N11" s="117" t="str">
         <f>IFERROR(INDEX('LISTA DE ESTUDIANTES'!$E$2:$E$102,MATCH($N$10,'LISTA DE ESTUDIANTES'!$B$2:$B$102, 0)), " ")</f>
         <v>Revisar Expediente</v>
       </c>
-      <c r="O11" s="130"/>
+      <c r="O11" s="118"/>
       <c r="P11" s="27">
         <f ca="1">+TODAY()</f>
-        <v>45815</v>
+        <v>46158</v>
       </c>
       <c r="Q11" s="8"/>
-      <c r="S11" s="87"/>
-      <c r="T11" s="88"/>
-      <c r="U11" s="88"/>
-      <c r="V11" s="89"/>
+      <c r="S11" s="109"/>
+      <c r="T11" s="110"/>
+      <c r="U11" s="110"/>
+      <c r="V11" s="111"/>
     </row>
     <row r="12" spans="1:22" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
@@ -6073,18 +6076,18 @@
       <c r="B12" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="99"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="100"/>
-      <c r="F12" s="101"/>
+      <c r="C12" s="134"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="136"/>
       <c r="G12" s="75"/>
       <c r="H12" s="75"/>
       <c r="J12" s="16"/>
-      <c r="K12" s="121" t="s">
+      <c r="K12" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="122"/>
-      <c r="M12" s="123"/>
+      <c r="L12" s="100"/>
+      <c r="M12" s="101"/>
       <c r="N12" s="19" t="s">
         <v>315</v>
       </c>
@@ -6095,10 +6098,10 @@
         <v>316</v>
       </c>
       <c r="Q12" s="8"/>
-      <c r="S12" s="87"/>
-      <c r="T12" s="88"/>
-      <c r="U12" s="88"/>
-      <c r="V12" s="89"/>
+      <c r="S12" s="109"/>
+      <c r="T12" s="110"/>
+      <c r="U12" s="110"/>
+      <c r="V12" s="111"/>
     </row>
     <row r="13" spans="1:22" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
@@ -6110,19 +6113,19 @@
       <c r="J13" s="16"/>
       <c r="K13" s="60"/>
       <c r="L13" s="60"/>
-      <c r="M13" s="120" t="s">
+      <c r="M13" s="141" t="s">
         <v>7</v>
       </c>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120" t="s">
+      <c r="N13" s="141"/>
+      <c r="O13" s="141" t="s">
         <v>5</v>
       </c>
-      <c r="P13" s="120"/>
+      <c r="P13" s="141"/>
       <c r="Q13" s="8"/>
-      <c r="S13" s="90"/>
-      <c r="T13" s="91"/>
-      <c r="U13" s="91"/>
-      <c r="V13" s="92"/>
+      <c r="S13" s="112"/>
+      <c r="T13" s="113"/>
+      <c r="U13" s="113"/>
+      <c r="V13" s="114"/>
     </row>
     <row r="14" spans="1:22" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
@@ -6132,21 +6135,21 @@
         <v>30</v>
       </c>
       <c r="J14" s="16"/>
-      <c r="K14" s="121" t="s">
+      <c r="K14" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="L14" s="122"/>
-      <c r="M14" s="122"/>
-      <c r="N14" s="122"/>
-      <c r="O14" s="122"/>
-      <c r="P14" s="123"/>
+      <c r="L14" s="100"/>
+      <c r="M14" s="100"/>
+      <c r="N14" s="100"/>
+      <c r="O14" s="100"/>
+      <c r="P14" s="101"/>
       <c r="Q14" s="8"/>
-      <c r="S14" s="84" t="s">
+      <c r="S14" s="106" t="s">
         <v>227</v>
       </c>
-      <c r="T14" s="85"/>
-      <c r="U14" s="85"/>
-      <c r="V14" s="86"/>
+      <c r="T14" s="107"/>
+      <c r="U14" s="107"/>
+      <c r="V14" s="108"/>
     </row>
     <row r="15" spans="1:22" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
@@ -6156,23 +6159,23 @@
         <v>32</v>
       </c>
       <c r="J15" s="16"/>
-      <c r="K15" s="126" t="s">
+      <c r="K15" s="144" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="127"/>
-      <c r="M15" s="124" t="s">
+      <c r="L15" s="145"/>
+      <c r="M15" s="142" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="125"/>
+      <c r="N15" s="143"/>
       <c r="O15" s="29" t="s">
         <v>12</v>
       </c>
       <c r="P15" s="30"/>
       <c r="Q15" s="8"/>
-      <c r="S15" s="87"/>
-      <c r="T15" s="88"/>
-      <c r="U15" s="88"/>
-      <c r="V15" s="89"/>
+      <c r="S15" s="109"/>
+      <c r="T15" s="110"/>
+      <c r="U15" s="110"/>
+      <c r="V15" s="111"/>
     </row>
     <row r="16" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
@@ -6182,22 +6185,22 @@
         <v>34</v>
       </c>
       <c r="J16" s="16"/>
-      <c r="K16" s="104" t="s">
+      <c r="K16" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="L16" s="105"/>
-      <c r="M16" s="108" t="str">
+      <c r="L16" s="84"/>
+      <c r="M16" s="87" t="str">
         <f>IFERROR(INDEX($B$6:$B$18, MATCH(K16, $A$6:$A$18, 0)), " ")</f>
         <v xml:space="preserve">Reforzar cada logro por más pequeño que este sea. </v>
       </c>
-      <c r="N16" s="109"/>
-      <c r="O16" s="112"/>
-      <c r="P16" s="113"/>
+      <c r="N16" s="88"/>
+      <c r="O16" s="91"/>
+      <c r="P16" s="92"/>
       <c r="Q16" s="8"/>
-      <c r="S16" s="87"/>
-      <c r="T16" s="88"/>
-      <c r="U16" s="88"/>
-      <c r="V16" s="89"/>
+      <c r="S16" s="109"/>
+      <c r="T16" s="110"/>
+      <c r="U16" s="110"/>
+      <c r="V16" s="111"/>
     </row>
     <row r="17" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
@@ -6207,17 +6210,17 @@
         <v>36</v>
       </c>
       <c r="J17" s="16"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="107"/>
-      <c r="M17" s="110"/>
-      <c r="N17" s="111"/>
-      <c r="O17" s="114"/>
-      <c r="P17" s="115"/>
+      <c r="K17" s="85"/>
+      <c r="L17" s="86"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="90"/>
+      <c r="O17" s="93"/>
+      <c r="P17" s="94"/>
       <c r="Q17" s="8"/>
-      <c r="S17" s="90"/>
-      <c r="T17" s="91"/>
-      <c r="U17" s="91"/>
-      <c r="V17" s="92"/>
+      <c r="S17" s="112"/>
+      <c r="T17" s="113"/>
+      <c r="U17" s="113"/>
+      <c r="V17" s="114"/>
     </row>
     <row r="18" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
@@ -6227,17 +6230,17 @@
         <v>38</v>
       </c>
       <c r="J18" s="16"/>
-      <c r="K18" s="104" t="s">
+      <c r="K18" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="L18" s="105"/>
-      <c r="M18" s="108" t="str">
+      <c r="L18" s="84"/>
+      <c r="M18" s="87" t="str">
         <f>IFERROR(INDEX($B$6:$B$18, MATCH(K18, $A$6:$A$18, 0)), " ")</f>
         <v xml:space="preserve">Brindar acercamiento físico y las manifestaciones de apoyo. </v>
       </c>
-      <c r="N18" s="109"/>
-      <c r="O18" s="112"/>
-      <c r="P18" s="113"/>
+      <c r="N18" s="88"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="92"/>
       <c r="Q18" s="8"/>
     </row>
     <row r="19" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6245,12 +6248,12 @@
         <v>111</v>
       </c>
       <c r="J19" s="16"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="107"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="111"/>
-      <c r="O19" s="114"/>
-      <c r="P19" s="115"/>
+      <c r="K19" s="85"/>
+      <c r="L19" s="86"/>
+      <c r="M19" s="89"/>
+      <c r="N19" s="90"/>
+      <c r="O19" s="93"/>
+      <c r="P19" s="94"/>
       <c r="Q19" s="8"/>
     </row>
     <row r="20" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6261,17 +6264,17 @@
         <v>56</v>
       </c>
       <c r="J20" s="16"/>
-      <c r="K20" s="104" t="s">
+      <c r="K20" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="L20" s="105"/>
-      <c r="M20" s="108" t="str">
+      <c r="L20" s="84"/>
+      <c r="M20" s="87" t="str">
         <f>IFERROR(INDEX($B$6:$B$18, MATCH(K20, $A$6:$A$18, 0)), " ")</f>
         <v xml:space="preserve">Utilizar la tutoría entre compañeros. </v>
       </c>
-      <c r="N20" s="109"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="113"/>
+      <c r="N20" s="88"/>
+      <c r="O20" s="91"/>
+      <c r="P20" s="92"/>
       <c r="Q20" s="8"/>
     </row>
     <row r="21" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6282,12 +6285,12 @@
         <v>58</v>
       </c>
       <c r="J21" s="16"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="107"/>
-      <c r="M21" s="110"/>
-      <c r="N21" s="111"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="115"/>
+      <c r="K21" s="85"/>
+      <c r="L21" s="86"/>
+      <c r="M21" s="89"/>
+      <c r="N21" s="90"/>
+      <c r="O21" s="93"/>
+      <c r="P21" s="94"/>
       <c r="Q21" s="8"/>
     </row>
     <row r="22" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6298,18 +6301,18 @@
         <v>60</v>
       </c>
       <c r="J22" s="16"/>
-      <c r="K22" s="104" t="s">
+      <c r="K22" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="105"/>
-      <c r="M22" s="135" t="s">
+      <c r="L22" s="84"/>
+      <c r="M22" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="N22" s="136"/>
-      <c r="O22" s="135" t="s">
+      <c r="N22" s="96"/>
+      <c r="O22" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="P22" s="136"/>
+      <c r="P22" s="96"/>
       <c r="Q22" s="8"/>
     </row>
     <row r="23" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6320,12 +6323,12 @@
         <v>62</v>
       </c>
       <c r="J23" s="16"/>
-      <c r="K23" s="106"/>
-      <c r="L23" s="107"/>
-      <c r="M23" s="137"/>
-      <c r="N23" s="138"/>
-      <c r="O23" s="137"/>
-      <c r="P23" s="138"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="86"/>
+      <c r="M23" s="97"/>
+      <c r="N23" s="98"/>
+      <c r="O23" s="97"/>
+      <c r="P23" s="98"/>
       <c r="Q23" s="8"/>
     </row>
     <row r="24" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6336,17 +6339,17 @@
         <v>64</v>
       </c>
       <c r="J24" s="16"/>
-      <c r="K24" s="104" t="s">
+      <c r="K24" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="L24" s="105"/>
-      <c r="M24" s="108" t="str">
+      <c r="L24" s="84"/>
+      <c r="M24" s="87" t="str">
         <f>IFERROR(INDEX($B$20:$B$30, MATCH(K24, $A$20:$A$30, 0)), " ")</f>
         <v>Sentar al estudiante en un lugar donde tenga buena iluminación</v>
       </c>
-      <c r="N24" s="109"/>
-      <c r="O24" s="112"/>
-      <c r="P24" s="113"/>
+      <c r="N24" s="88"/>
+      <c r="O24" s="91"/>
+      <c r="P24" s="92"/>
       <c r="Q24" s="8"/>
     </row>
     <row r="25" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6357,12 +6360,12 @@
         <v>66</v>
       </c>
       <c r="J25" s="16"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="107"/>
-      <c r="M25" s="110"/>
-      <c r="N25" s="111"/>
-      <c r="O25" s="114"/>
-      <c r="P25" s="115"/>
+      <c r="K25" s="85"/>
+      <c r="L25" s="86"/>
+      <c r="M25" s="89"/>
+      <c r="N25" s="90"/>
+      <c r="O25" s="93"/>
+      <c r="P25" s="94"/>
       <c r="Q25" s="8"/>
     </row>
     <row r="26" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6373,17 +6376,17 @@
         <v>68</v>
       </c>
       <c r="J26" s="16"/>
-      <c r="K26" s="104" t="s">
+      <c r="K26" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="L26" s="105"/>
-      <c r="M26" s="108" t="str">
+      <c r="L26" s="84"/>
+      <c r="M26" s="87" t="str">
         <f t="shared" ref="M26" si="0">IFERROR(INDEX($B$20:$B$30, MATCH(K26, $A$20:$A$30, 0)), " ")</f>
         <v>Organizar el tiempo y del espacio para mejorar el clima organizacional.</v>
       </c>
-      <c r="N26" s="109"/>
-      <c r="O26" s="112"/>
-      <c r="P26" s="113"/>
+      <c r="N26" s="88"/>
+      <c r="O26" s="91"/>
+      <c r="P26" s="92"/>
       <c r="Q26" s="8"/>
     </row>
     <row r="27" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6394,12 +6397,12 @@
         <v>70</v>
       </c>
       <c r="J27" s="16"/>
-      <c r="K27" s="106"/>
-      <c r="L27" s="107"/>
-      <c r="M27" s="110"/>
-      <c r="N27" s="111"/>
-      <c r="O27" s="114"/>
-      <c r="P27" s="115"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="86"/>
+      <c r="M27" s="89"/>
+      <c r="N27" s="90"/>
+      <c r="O27" s="93"/>
+      <c r="P27" s="94"/>
       <c r="Q27" s="8"/>
     </row>
     <row r="28" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6410,17 +6413,17 @@
         <v>72</v>
       </c>
       <c r="J28" s="16"/>
-      <c r="K28" s="104" t="s">
+      <c r="K28" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="L28" s="105"/>
-      <c r="M28" s="108" t="str">
+      <c r="L28" s="84"/>
+      <c r="M28" s="87" t="str">
         <f t="shared" ref="M28" si="1">IFERROR(INDEX($B$20:$B$30, MATCH(K28, $A$20:$A$30, 0)), " ")</f>
         <v>Ubicar al estudiante cerca de compañeros que no se desconcentren.</v>
       </c>
-      <c r="N28" s="109"/>
-      <c r="O28" s="112"/>
-      <c r="P28" s="113"/>
+      <c r="N28" s="88"/>
+      <c r="O28" s="91"/>
+      <c r="P28" s="92"/>
       <c r="Q28" s="8"/>
     </row>
     <row r="29" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6431,12 +6434,12 @@
         <v>74</v>
       </c>
       <c r="J29" s="16"/>
-      <c r="K29" s="106"/>
-      <c r="L29" s="107"/>
-      <c r="M29" s="110"/>
-      <c r="N29" s="111"/>
-      <c r="O29" s="114"/>
-      <c r="P29" s="115"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="86"/>
+      <c r="M29" s="89"/>
+      <c r="N29" s="90"/>
+      <c r="O29" s="93"/>
+      <c r="P29" s="94"/>
       <c r="Q29" s="8"/>
     </row>
     <row r="30" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6447,28 +6450,28 @@
         <v>76</v>
       </c>
       <c r="J30" s="16"/>
-      <c r="K30" s="104" t="s">
+      <c r="K30" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="L30" s="105"/>
-      <c r="M30" s="135" t="s">
+      <c r="L30" s="84"/>
+      <c r="M30" s="95" t="s">
         <v>112</v>
       </c>
-      <c r="N30" s="136"/>
-      <c r="O30" s="135" t="s">
+      <c r="N30" s="96"/>
+      <c r="O30" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="P30" s="136"/>
+      <c r="P30" s="96"/>
       <c r="Q30" s="8"/>
     </row>
     <row r="31" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J31" s="16"/>
-      <c r="K31" s="106"/>
-      <c r="L31" s="107"/>
-      <c r="M31" s="137"/>
-      <c r="N31" s="138"/>
-      <c r="O31" s="137"/>
-      <c r="P31" s="138"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="86"/>
+      <c r="M31" s="97"/>
+      <c r="N31" s="98"/>
+      <c r="O31" s="97"/>
+      <c r="P31" s="98"/>
       <c r="Q31" s="8"/>
     </row>
     <row r="32" spans="1:22" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6477,17 +6480,17 @@
         <v>77</v>
       </c>
       <c r="J32" s="16"/>
-      <c r="K32" s="104" t="s">
+      <c r="K32" s="83" t="s">
         <v>89</v>
       </c>
-      <c r="L32" s="105"/>
-      <c r="M32" s="108" t="str">
+      <c r="L32" s="84"/>
+      <c r="M32" s="87" t="str">
         <f>IFERROR(INDEX($B$33:$B$49, MATCH(K32, $A$33:$A$49, 0)), " ")</f>
         <v>Usar láminas, mapas, gráficos y vídeos relacionados con los aprendizajes que se desarrollan.</v>
       </c>
-      <c r="N32" s="109"/>
-      <c r="O32" s="112"/>
-      <c r="P32" s="113"/>
+      <c r="N32" s="88"/>
+      <c r="O32" s="91"/>
+      <c r="P32" s="92"/>
       <c r="Q32" s="8"/>
     </row>
     <row r="33" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6498,12 +6501,12 @@
         <v>78</v>
       </c>
       <c r="J33" s="16"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="107"/>
-      <c r="M33" s="110"/>
-      <c r="N33" s="111"/>
-      <c r="O33" s="114"/>
-      <c r="P33" s="115"/>
+      <c r="K33" s="85"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="89"/>
+      <c r="N33" s="90"/>
+      <c r="O33" s="93"/>
+      <c r="P33" s="94"/>
       <c r="Q33" s="8"/>
     </row>
     <row r="34" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6514,17 +6517,17 @@
         <v>80</v>
       </c>
       <c r="J34" s="16"/>
-      <c r="K34" s="104" t="s">
+      <c r="K34" s="83" t="s">
         <v>103</v>
       </c>
-      <c r="L34" s="105"/>
-      <c r="M34" s="108" t="str">
+      <c r="L34" s="84"/>
+      <c r="M34" s="87" t="str">
         <f>IFERROR(INDEX($B$33:$B$49, MATCH(K34, $A$33:$A$49, 0)), " ")</f>
         <v>Facilitar material de reforzamiento para hacer en casa.</v>
       </c>
-      <c r="N34" s="109"/>
-      <c r="O34" s="112"/>
-      <c r="P34" s="113"/>
+      <c r="N34" s="88"/>
+      <c r="O34" s="91"/>
+      <c r="P34" s="92"/>
       <c r="Q34" s="8"/>
     </row>
     <row r="35" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6535,12 +6538,12 @@
         <v>82</v>
       </c>
       <c r="J35" s="16"/>
-      <c r="K35" s="106"/>
-      <c r="L35" s="107"/>
-      <c r="M35" s="110"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="114"/>
-      <c r="P35" s="115"/>
+      <c r="K35" s="85"/>
+      <c r="L35" s="86"/>
+      <c r="M35" s="89"/>
+      <c r="N35" s="90"/>
+      <c r="O35" s="93"/>
+      <c r="P35" s="94"/>
       <c r="Q35" s="8"/>
     </row>
     <row r="36" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6551,17 +6554,17 @@
         <v>84</v>
       </c>
       <c r="J36" s="16"/>
-      <c r="K36" s="104" t="s">
+      <c r="K36" s="83" t="s">
         <v>75</v>
       </c>
-      <c r="L36" s="105"/>
-      <c r="M36" s="108" t="str">
+      <c r="L36" s="84"/>
+      <c r="M36" s="87" t="str">
         <f>IFERROR(INDEX($B$33:$B$49, MATCH(K36, $A$33:$A$49, 0)), " ")</f>
         <v>Ampliar la letra al tamaño que el estudiante sienta mejor.</v>
       </c>
-      <c r="N36" s="109"/>
-      <c r="O36" s="112"/>
-      <c r="P36" s="113"/>
+      <c r="N36" s="88"/>
+      <c r="O36" s="91"/>
+      <c r="P36" s="92"/>
       <c r="Q36" s="8"/>
     </row>
     <row r="37" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6572,12 +6575,12 @@
         <v>86</v>
       </c>
       <c r="J37" s="16"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="107"/>
-      <c r="M37" s="110"/>
-      <c r="N37" s="111"/>
-      <c r="O37" s="114"/>
-      <c r="P37" s="115"/>
+      <c r="K37" s="85"/>
+      <c r="L37" s="86"/>
+      <c r="M37" s="89"/>
+      <c r="N37" s="90"/>
+      <c r="O37" s="93"/>
+      <c r="P37" s="94"/>
       <c r="Q37" s="8"/>
     </row>
     <row r="38" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6628,18 +6631,18 @@
         <v>94</v>
       </c>
       <c r="J41" s="16"/>
-      <c r="K41" s="104" t="s">
+      <c r="K41" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="L41" s="105"/>
-      <c r="M41" s="135" t="s">
+      <c r="L41" s="84"/>
+      <c r="M41" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="N41" s="136"/>
-      <c r="O41" s="135" t="s">
+      <c r="N41" s="96"/>
+      <c r="O41" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="P41" s="136"/>
+      <c r="P41" s="96"/>
       <c r="Q41" s="8"/>
     </row>
     <row r="42" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6650,12 +6653,12 @@
         <v>96</v>
       </c>
       <c r="J42" s="16"/>
-      <c r="K42" s="106"/>
-      <c r="L42" s="107"/>
-      <c r="M42" s="137"/>
-      <c r="N42" s="138"/>
-      <c r="O42" s="137"/>
-      <c r="P42" s="138"/>
+      <c r="K42" s="85"/>
+      <c r="L42" s="86"/>
+      <c r="M42" s="97"/>
+      <c r="N42" s="98"/>
+      <c r="O42" s="97"/>
+      <c r="P42" s="98"/>
       <c r="Q42" s="8"/>
     </row>
     <row r="43" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6666,17 +6669,17 @@
         <v>98</v>
       </c>
       <c r="J43" s="16"/>
-      <c r="K43" s="104" t="s">
+      <c r="K43" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="L43" s="105"/>
-      <c r="M43" s="108" t="str">
+      <c r="L43" s="84"/>
+      <c r="M43" s="87" t="str">
         <f>IFERROR(INDEX($B$53:$B$87, MATCH(K43, $A$53:$A$87, 0)), " ")</f>
         <v>Hablar siempre frente al estudiante (contacto visual).</v>
       </c>
-      <c r="N43" s="109"/>
-      <c r="O43" s="112"/>
-      <c r="P43" s="113"/>
+      <c r="N43" s="88"/>
+      <c r="O43" s="91"/>
+      <c r="P43" s="92"/>
       <c r="Q43" s="8"/>
     </row>
     <row r="44" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6687,12 +6690,12 @@
         <v>100</v>
       </c>
       <c r="J44" s="16"/>
-      <c r="K44" s="106"/>
-      <c r="L44" s="107"/>
-      <c r="M44" s="110"/>
-      <c r="N44" s="111"/>
-      <c r="O44" s="114"/>
-      <c r="P44" s="115"/>
+      <c r="K44" s="85"/>
+      <c r="L44" s="86"/>
+      <c r="M44" s="89"/>
+      <c r="N44" s="90"/>
+      <c r="O44" s="93"/>
+      <c r="P44" s="94"/>
       <c r="Q44" s="8"/>
     </row>
     <row r="45" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6703,17 +6706,17 @@
         <v>102</v>
       </c>
       <c r="J45" s="16"/>
-      <c r="K45" s="104" t="s">
+      <c r="K45" s="83" t="s">
         <v>126</v>
       </c>
-      <c r="L45" s="105"/>
-      <c r="M45" s="108" t="str">
+      <c r="L45" s="84"/>
+      <c r="M45" s="87" t="str">
         <f t="shared" ref="M45" si="2">IFERROR(INDEX($B$53:$B$87, MATCH(K45, $A$53:$A$87, 0)), " ")</f>
         <v>De ser necesario disminuir la longitud y la cantidad de las tareas y/o actividades.</v>
       </c>
-      <c r="N45" s="109"/>
-      <c r="O45" s="112"/>
-      <c r="P45" s="113"/>
+      <c r="N45" s="88"/>
+      <c r="O45" s="91"/>
+      <c r="P45" s="92"/>
       <c r="Q45" s="8"/>
     </row>
     <row r="46" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6724,12 +6727,12 @@
         <v>104</v>
       </c>
       <c r="J46" s="16"/>
-      <c r="K46" s="106"/>
-      <c r="L46" s="107"/>
-      <c r="M46" s="110"/>
-      <c r="N46" s="111"/>
-      <c r="O46" s="114"/>
-      <c r="P46" s="115"/>
+      <c r="K46" s="85"/>
+      <c r="L46" s="86"/>
+      <c r="M46" s="89"/>
+      <c r="N46" s="90"/>
+      <c r="O46" s="93"/>
+      <c r="P46" s="94"/>
       <c r="Q46" s="8"/>
     </row>
     <row r="47" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6740,17 +6743,17 @@
         <v>106</v>
       </c>
       <c r="J47" s="16"/>
-      <c r="K47" s="104" t="s">
+      <c r="K47" s="83" t="s">
         <v>174</v>
       </c>
-      <c r="L47" s="105"/>
-      <c r="M47" s="108" t="str">
+      <c r="L47" s="84"/>
+      <c r="M47" s="87" t="str">
         <f t="shared" ref="M47" si="3">IFERROR(INDEX($B$53:$B$87, MATCH(K47, $A$53:$A$87, 0)), " ")</f>
         <v>Establecer rutinas de trabajo.</v>
       </c>
-      <c r="N47" s="109"/>
-      <c r="O47" s="112"/>
-      <c r="P47" s="113"/>
+      <c r="N47" s="88"/>
+      <c r="O47" s="91"/>
+      <c r="P47" s="92"/>
       <c r="Q47" s="8"/>
     </row>
     <row r="48" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6761,12 +6764,12 @@
         <v>108</v>
       </c>
       <c r="J48" s="16"/>
-      <c r="K48" s="106"/>
-      <c r="L48" s="107"/>
-      <c r="M48" s="110"/>
-      <c r="N48" s="111"/>
-      <c r="O48" s="114"/>
-      <c r="P48" s="115"/>
+      <c r="K48" s="85"/>
+      <c r="L48" s="86"/>
+      <c r="M48" s="89"/>
+      <c r="N48" s="90"/>
+      <c r="O48" s="93"/>
+      <c r="P48" s="94"/>
       <c r="Q48" s="8"/>
     </row>
     <row r="49" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -6777,43 +6780,43 @@
         <v>76</v>
       </c>
       <c r="J49" s="16"/>
-      <c r="K49" s="104" t="s">
+      <c r="K49" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="L49" s="105"/>
-      <c r="M49" s="135" t="s">
+      <c r="L49" s="84"/>
+      <c r="M49" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="N49" s="136"/>
-      <c r="O49" s="135" t="s">
+      <c r="N49" s="96"/>
+      <c r="O49" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="P49" s="136"/>
+      <c r="P49" s="96"/>
       <c r="Q49" s="8"/>
     </row>
     <row r="50" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J50" s="16"/>
-      <c r="K50" s="106"/>
-      <c r="L50" s="107"/>
-      <c r="M50" s="137"/>
-      <c r="N50" s="138"/>
-      <c r="O50" s="137"/>
-      <c r="P50" s="138"/>
+      <c r="K50" s="85"/>
+      <c r="L50" s="86"/>
+      <c r="M50" s="97"/>
+      <c r="N50" s="98"/>
+      <c r="O50" s="97"/>
+      <c r="P50" s="98"/>
       <c r="Q50" s="8"/>
     </row>
     <row r="51" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J51" s="16"/>
-      <c r="K51" s="104" t="s">
+      <c r="K51" s="83" t="s">
         <v>208</v>
       </c>
-      <c r="L51" s="105"/>
-      <c r="M51" s="108" t="str">
+      <c r="L51" s="84"/>
+      <c r="M51" s="87" t="str">
         <f>IFERROR(INDEX($B$90:$B$104, MATCH(K51, $A$90:$A$104, 0)), " ")</f>
         <v>Usar la calculadora.</v>
       </c>
-      <c r="N51" s="109"/>
-      <c r="O51" s="112"/>
-      <c r="P51" s="113"/>
+      <c r="N51" s="88"/>
+      <c r="O51" s="91"/>
+      <c r="P51" s="92"/>
       <c r="Q51" s="8"/>
     </row>
     <row r="52" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6822,12 +6825,12 @@
         <v>113</v>
       </c>
       <c r="J52" s="6"/>
-      <c r="K52" s="106"/>
-      <c r="L52" s="107"/>
-      <c r="M52" s="110"/>
-      <c r="N52" s="111"/>
-      <c r="O52" s="114"/>
-      <c r="P52" s="115"/>
+      <c r="K52" s="85"/>
+      <c r="L52" s="86"/>
+      <c r="M52" s="89"/>
+      <c r="N52" s="90"/>
+      <c r="O52" s="93"/>
+      <c r="P52" s="94"/>
       <c r="Q52" s="2"/>
     </row>
     <row r="53" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6838,17 +6841,17 @@
         <v>115</v>
       </c>
       <c r="J53" s="6"/>
-      <c r="K53" s="104" t="s">
+      <c r="K53" s="83" t="s">
         <v>198</v>
       </c>
-      <c r="L53" s="105"/>
-      <c r="M53" s="108" t="str">
+      <c r="L53" s="84"/>
+      <c r="M53" s="87" t="str">
         <f t="shared" ref="M53" si="4">IFERROR(INDEX($B$90:$B$104, MATCH(K53, $A$90:$A$104, 0)), " ")</f>
         <v>Aplicar evaluaciones cortas y frecuentes.</v>
       </c>
-      <c r="N53" s="109"/>
-      <c r="O53" s="112"/>
-      <c r="P53" s="113"/>
+      <c r="N53" s="88"/>
+      <c r="O53" s="91"/>
+      <c r="P53" s="92"/>
       <c r="Q53" s="2"/>
     </row>
     <row r="54" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6859,12 +6862,12 @@
         <v>117</v>
       </c>
       <c r="J54" s="6"/>
-      <c r="K54" s="106"/>
-      <c r="L54" s="107"/>
-      <c r="M54" s="110"/>
-      <c r="N54" s="111"/>
-      <c r="O54" s="114"/>
-      <c r="P54" s="115"/>
+      <c r="K54" s="85"/>
+      <c r="L54" s="86"/>
+      <c r="M54" s="89"/>
+      <c r="N54" s="90"/>
+      <c r="O54" s="93"/>
+      <c r="P54" s="94"/>
       <c r="Q54" s="2"/>
     </row>
     <row r="55" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6875,17 +6878,17 @@
         <v>119</v>
       </c>
       <c r="J55" s="6"/>
-      <c r="K55" s="104" t="s">
+      <c r="K55" s="83" t="s">
         <v>208</v>
       </c>
-      <c r="L55" s="105"/>
-      <c r="M55" s="108" t="str">
+      <c r="L55" s="84"/>
+      <c r="M55" s="87" t="str">
         <f t="shared" ref="M55" si="5">IFERROR(INDEX($B$90:$B$104, MATCH(K55, $A$90:$A$104, 0)), " ")</f>
         <v>Usar la calculadora.</v>
       </c>
-      <c r="N55" s="109"/>
-      <c r="O55" s="112"/>
-      <c r="P55" s="113"/>
+      <c r="N55" s="88"/>
+      <c r="O55" s="91"/>
+      <c r="P55" s="92"/>
       <c r="Q55" s="2"/>
     </row>
     <row r="56" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6896,12 +6899,12 @@
         <v>121</v>
       </c>
       <c r="J56" s="6"/>
-      <c r="K56" s="106"/>
-      <c r="L56" s="107"/>
-      <c r="M56" s="110"/>
-      <c r="N56" s="111"/>
-      <c r="O56" s="114"/>
-      <c r="P56" s="115"/>
+      <c r="K56" s="85"/>
+      <c r="L56" s="86"/>
+      <c r="M56" s="89"/>
+      <c r="N56" s="90"/>
+      <c r="O56" s="93"/>
+      <c r="P56" s="94"/>
       <c r="Q56" s="2"/>
     </row>
     <row r="57" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6928,14 +6931,14 @@
         <v>125</v>
       </c>
       <c r="J58" s="6"/>
-      <c r="K58" s="144" t="s">
+      <c r="K58" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="L58" s="144"/>
-      <c r="M58" s="144"/>
-      <c r="N58" s="144"/>
-      <c r="O58" s="144"/>
-      <c r="P58" s="144"/>
+      <c r="L58" s="81"/>
+      <c r="M58" s="81"/>
+      <c r="N58" s="81"/>
+      <c r="O58" s="81"/>
+      <c r="P58" s="81"/>
       <c r="Q58" s="2"/>
     </row>
     <row r="59" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6946,11 +6949,11 @@
         <v>127</v>
       </c>
       <c r="J59" s="6"/>
-      <c r="K59" s="145" t="s">
+      <c r="K59" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="L59" s="145"/>
-      <c r="M59" s="145"/>
+      <c r="L59" s="82"/>
+      <c r="M59" s="82"/>
       <c r="N59" s="31" t="s">
         <v>47</v>
       </c>
@@ -7006,12 +7009,12 @@
         <v>133</v>
       </c>
       <c r="J62" s="6"/>
-      <c r="K62" s="139"/>
-      <c r="L62" s="140"/>
-      <c r="M62" s="140"/>
-      <c r="N62" s="140"/>
-      <c r="O62" s="140"/>
-      <c r="P62" s="141"/>
+      <c r="K62" s="76"/>
+      <c r="L62" s="77"/>
+      <c r="M62" s="77"/>
+      <c r="N62" s="77"/>
+      <c r="O62" s="77"/>
+      <c r="P62" s="78"/>
       <c r="Q62" s="2"/>
     </row>
     <row r="63" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7022,12 +7025,12 @@
         <v>135</v>
       </c>
       <c r="J63" s="6"/>
-      <c r="K63" s="139"/>
-      <c r="L63" s="140"/>
-      <c r="M63" s="140"/>
-      <c r="N63" s="140"/>
-      <c r="O63" s="140"/>
-      <c r="P63" s="141"/>
+      <c r="K63" s="76"/>
+      <c r="L63" s="77"/>
+      <c r="M63" s="77"/>
+      <c r="N63" s="77"/>
+      <c r="O63" s="77"/>
+      <c r="P63" s="78"/>
       <c r="Q63" s="2"/>
     </row>
     <row r="64" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7038,12 +7041,12 @@
         <v>137</v>
       </c>
       <c r="J64" s="6"/>
-      <c r="K64" s="139"/>
-      <c r="L64" s="140"/>
-      <c r="M64" s="140"/>
-      <c r="N64" s="140"/>
-      <c r="O64" s="140"/>
-      <c r="P64" s="141"/>
+      <c r="K64" s="76"/>
+      <c r="L64" s="77"/>
+      <c r="M64" s="77"/>
+      <c r="N64" s="77"/>
+      <c r="O64" s="77"/>
+      <c r="P64" s="78"/>
       <c r="Q64" s="8"/>
     </row>
     <row r="65" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7090,17 +7093,17 @@
         <v>143</v>
       </c>
       <c r="J67" s="6"/>
-      <c r="K67" s="142" t="s">
+      <c r="K67" s="79" t="s">
         <v>49</v>
       </c>
-      <c r="L67" s="142"/>
-      <c r="M67" s="142"/>
-      <c r="N67" s="142"/>
-      <c r="O67" s="142" t="s">
+      <c r="L67" s="79"/>
+      <c r="M67" s="79"/>
+      <c r="N67" s="79"/>
+      <c r="O67" s="79" t="s">
         <v>51</v>
       </c>
-      <c r="P67" s="142"/>
-      <c r="Q67" s="143"/>
+      <c r="P67" s="79"/>
+      <c r="Q67" s="80"/>
     </row>
     <row r="68" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="13" t="s">
@@ -7192,15 +7195,15 @@
         <v>155</v>
       </c>
       <c r="J73" s="6"/>
-      <c r="K73" s="102" t="s">
+      <c r="K73" s="137" t="s">
         <v>53</v>
       </c>
-      <c r="L73" s="102"/>
-      <c r="M73" s="102"/>
-      <c r="N73" s="102"/>
-      <c r="O73" s="102"/>
-      <c r="P73" s="102"/>
-      <c r="Q73" s="103"/>
+      <c r="L73" s="137"/>
+      <c r="M73" s="137"/>
+      <c r="N73" s="137"/>
+      <c r="O73" s="137"/>
+      <c r="P73" s="137"/>
+      <c r="Q73" s="138"/>
     </row>
     <row r="74" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="13" t="s">
@@ -7212,12 +7215,12 @@
       <c r="J74" s="9"/>
       <c r="K74" s="10"/>
       <c r="L74" s="10"/>
-      <c r="M74" s="128" t="s">
+      <c r="M74" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="N74" s="128"/>
-      <c r="O74" s="128"/>
-      <c r="P74" s="128"/>
+      <c r="N74" s="105"/>
+      <c r="O74" s="105"/>
+      <c r="P74" s="105"/>
       <c r="Q74" s="11"/>
     </row>
     <row r="75" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7548,81 +7551,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="TZ2GIgc+/GCtl/EnGbpqyNzBabNY+ThsrI4pBI7/yNykn/OakjiUwYI3G8imVfDwTFeC5yBw1reR9TobeyHzEA==" saltValue="u5O4E4/F8PQaZyB6KZHOwA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="85">
-    <mergeCell ref="K73:Q73"/>
-    <mergeCell ref="M74:P74"/>
-    <mergeCell ref="K58:P58"/>
-    <mergeCell ref="K59:M59"/>
-    <mergeCell ref="K62:P62"/>
-    <mergeCell ref="K63:P63"/>
-    <mergeCell ref="K64:P64"/>
-    <mergeCell ref="K67:N67"/>
-    <mergeCell ref="O67:Q67"/>
-    <mergeCell ref="K53:L54"/>
-    <mergeCell ref="M53:N54"/>
-    <mergeCell ref="O53:P54"/>
-    <mergeCell ref="K55:L56"/>
-    <mergeCell ref="M55:N56"/>
-    <mergeCell ref="O55:P56"/>
-    <mergeCell ref="K49:L50"/>
-    <mergeCell ref="M49:N50"/>
-    <mergeCell ref="O49:P50"/>
-    <mergeCell ref="K51:L52"/>
-    <mergeCell ref="M51:N52"/>
-    <mergeCell ref="O51:P52"/>
-    <mergeCell ref="K45:L46"/>
-    <mergeCell ref="M45:N46"/>
-    <mergeCell ref="O45:P46"/>
-    <mergeCell ref="K47:L48"/>
-    <mergeCell ref="M47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="K41:L42"/>
-    <mergeCell ref="M41:N42"/>
-    <mergeCell ref="O41:P42"/>
-    <mergeCell ref="K43:L44"/>
-    <mergeCell ref="M43:N44"/>
-    <mergeCell ref="O43:P44"/>
-    <mergeCell ref="K34:L35"/>
-    <mergeCell ref="M34:N35"/>
-    <mergeCell ref="O34:P35"/>
-    <mergeCell ref="K36:L37"/>
-    <mergeCell ref="M36:N37"/>
-    <mergeCell ref="O36:P37"/>
-    <mergeCell ref="K30:L31"/>
-    <mergeCell ref="M30:N31"/>
-    <mergeCell ref="O30:P31"/>
-    <mergeCell ref="K32:L33"/>
-    <mergeCell ref="M32:N33"/>
-    <mergeCell ref="O32:P33"/>
-    <mergeCell ref="K26:L27"/>
-    <mergeCell ref="M26:N27"/>
-    <mergeCell ref="O26:P27"/>
-    <mergeCell ref="K28:L29"/>
-    <mergeCell ref="M28:N29"/>
-    <mergeCell ref="O28:P29"/>
-    <mergeCell ref="K22:L23"/>
-    <mergeCell ref="M22:N23"/>
-    <mergeCell ref="O22:P23"/>
-    <mergeCell ref="K24:L25"/>
-    <mergeCell ref="M24:N25"/>
-    <mergeCell ref="O24:P25"/>
-    <mergeCell ref="K18:L19"/>
-    <mergeCell ref="M18:N19"/>
-    <mergeCell ref="O18:P19"/>
-    <mergeCell ref="K20:L21"/>
-    <mergeCell ref="M20:N21"/>
-    <mergeCell ref="O20:P21"/>
-    <mergeCell ref="S14:V17"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="K16:L17"/>
-    <mergeCell ref="M16:N17"/>
-    <mergeCell ref="O16:P17"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="K14:P14"/>
     <mergeCell ref="N1:O3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C5:F8"/>
@@ -7633,6 +7561,81 @@
     <mergeCell ref="K10:M10"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="S10:V13"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="S14:V17"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="K16:L17"/>
+    <mergeCell ref="M16:N17"/>
+    <mergeCell ref="O16:P17"/>
+    <mergeCell ref="K14:P14"/>
+    <mergeCell ref="K18:L19"/>
+    <mergeCell ref="M18:N19"/>
+    <mergeCell ref="O18:P19"/>
+    <mergeCell ref="K20:L21"/>
+    <mergeCell ref="M20:N21"/>
+    <mergeCell ref="O20:P21"/>
+    <mergeCell ref="K22:L23"/>
+    <mergeCell ref="M22:N23"/>
+    <mergeCell ref="O22:P23"/>
+    <mergeCell ref="K24:L25"/>
+    <mergeCell ref="M24:N25"/>
+    <mergeCell ref="O24:P25"/>
+    <mergeCell ref="K26:L27"/>
+    <mergeCell ref="M26:N27"/>
+    <mergeCell ref="O26:P27"/>
+    <mergeCell ref="K28:L29"/>
+    <mergeCell ref="M28:N29"/>
+    <mergeCell ref="O28:P29"/>
+    <mergeCell ref="K30:L31"/>
+    <mergeCell ref="M30:N31"/>
+    <mergeCell ref="O30:P31"/>
+    <mergeCell ref="K32:L33"/>
+    <mergeCell ref="M32:N33"/>
+    <mergeCell ref="O32:P33"/>
+    <mergeCell ref="K34:L35"/>
+    <mergeCell ref="M34:N35"/>
+    <mergeCell ref="O34:P35"/>
+    <mergeCell ref="K36:L37"/>
+    <mergeCell ref="M36:N37"/>
+    <mergeCell ref="O36:P37"/>
+    <mergeCell ref="K41:L42"/>
+    <mergeCell ref="M41:N42"/>
+    <mergeCell ref="O41:P42"/>
+    <mergeCell ref="K43:L44"/>
+    <mergeCell ref="M43:N44"/>
+    <mergeCell ref="O43:P44"/>
+    <mergeCell ref="K45:L46"/>
+    <mergeCell ref="M45:N46"/>
+    <mergeCell ref="O45:P46"/>
+    <mergeCell ref="K47:L48"/>
+    <mergeCell ref="M47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="K49:L50"/>
+    <mergeCell ref="M49:N50"/>
+    <mergeCell ref="O49:P50"/>
+    <mergeCell ref="K51:L52"/>
+    <mergeCell ref="M51:N52"/>
+    <mergeCell ref="O51:P52"/>
+    <mergeCell ref="K53:L54"/>
+    <mergeCell ref="M53:N54"/>
+    <mergeCell ref="O53:P54"/>
+    <mergeCell ref="K55:L56"/>
+    <mergeCell ref="M55:N56"/>
+    <mergeCell ref="O55:P56"/>
+    <mergeCell ref="K73:Q73"/>
+    <mergeCell ref="M74:P74"/>
+    <mergeCell ref="K58:P58"/>
+    <mergeCell ref="K59:M59"/>
+    <mergeCell ref="K62:P62"/>
+    <mergeCell ref="K63:P63"/>
+    <mergeCell ref="K64:P64"/>
+    <mergeCell ref="K67:N67"/>
+    <mergeCell ref="O67:Q67"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K32:L38" xr:uid="{141316F3-3BD1-4B73-9460-FF020AB5E01F}">
